--- a/temp/MACRO_VISA_20250421.xlsx
+++ b/temp/MACRO_VISA_20250421.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>MACRO VISA</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>MACRO VISA</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>MACRO VISA</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>MACRO VISA</t>
         </is>
       </c>
     </row>

--- a/temp/MACRO_VISA_20250421.xlsx
+++ b/temp/MACRO_VISA_20250421.xlsx
@@ -471,12 +471,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>-1011305.27</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-1011305,27</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MACRO VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -496,12 +498,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>1827187.41</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1827187,41</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MACRO VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -521,12 +525,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>55000</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>55000,0</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MACRO VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -546,12 +552,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>70153.97</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>70153,97</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MACRO VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>

--- a/temp/MACRO_VISA_20250421.xlsx
+++ b/temp/MACRO_VISA_20250421.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>406818K MERPAGO*4PRODUCTOS</t>
+          <t>MERPAGO*4PRODUCTOS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>406819K MERPAGO*JONATANVALVERD</t>
+          <t>MERPAGO*JONATANVALVERD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>848527K MERPAGO*CAMINOAUSTRALIMPO</t>
+          <t>MERPAGO*CAMINOAUSTRALIMPO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
